--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2026 artfynd.xlsx
+++ b/artfynd/A 31881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305950</v>
       </c>
       <c r="B2" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137305748</v>
       </c>
       <c r="B3" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>137305758</v>
       </c>
       <c r="B4" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137305782</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
